--- a/consent_forms/029_junior_team_tennis_medical_release_and_consent_form--consent_forms.xlsx
+++ b/consent_forms/029_junior_team_tennis_medical_release_and_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1236,17 +1236,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medical_history_conditions_choices</t>
+          <t>medical_history_medications_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>antibiotics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Antibiotics</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>antibiotics</t>
+          <t>anti-inflammatory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Antibiotics</t>
+          <t>Anti-inflammatory</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>anti-inflammatory</t>
+          <t>blood_thinners</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Anti-inflammatory</t>
+          <t>Blood thinners</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>blood_thinners</t>
+          <t>cholesterol</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blood thinners</t>
+          <t>Cholesterol</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cholesterol</t>
+          <t>corticosteroid</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cholesterol</t>
+          <t>Corticosteroid</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>corticosteroid</t>
+          <t>epilepsy_medication</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Corticosteroid</t>
+          <t>Epilepsy medication</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>epilepsy_medication</t>
+          <t>insulin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Epilepsy medication</t>
+          <t>Insulin</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>insulin</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Insulin</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>prescription</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Prescription</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prescription</t>
+          <t>steroid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prescription</t>
+          <t>Steroid</t>
         </is>
       </c>
     </row>
@@ -1411,29 +1411,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>steroid</t>
+          <t>thyroid_medication</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Steroid</t>
+          <t>Thyroid medication</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>medical_history_medications_choices</t>
+          <t>medical_history_surgery_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>thyroid_medication</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thyroid medication</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>anesthesia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Anesthesia</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>anesthesia</t>
+          <t>artificial_joints</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Anesthesia</t>
+          <t>Artificial joints</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>artificial_joints</t>
+          <t>back_surgery</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Artificial joints</t>
+          <t>Back surgery</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>back_surgery</t>
+          <t>brain_surgery</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Back surgery</t>
+          <t>Brain surgery</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>brain_surgery</t>
+          <t>heart_surgery</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brain surgery</t>
+          <t>Heart surgery</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>heart_surgery</t>
+          <t>knee_replacement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Heart surgery</t>
+          <t>Knee replacement</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>knee_replacement</t>
+          <t>neurosurgery</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Knee replacement</t>
+          <t>Neurosurgery</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>neurosurgery</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neurosurgery</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>shoulder_surgery</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Shoulder surgery</t>
         </is>
       </c>
     </row>
@@ -1598,80 +1598,80 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>shoulder_surgery</t>
+          <t>tumor_surgery</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shoulder surgery</t>
+          <t>Tumor surgery</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>medical_history_surgery_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tumor_surgery</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tumor surgery</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>medical_history_surgery_choices</t>
+          <t>consent_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1700,44 +1700,10 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Friend</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
         <is>
           <t>Other (please specify)</t>
         </is>
